--- a/Sindhi Muslim/3rd Quarter Required Data/QPR/Shafi Muhammad Goth/H. Staff Attendance/Staff Attendance.xlsx
+++ b/Sindhi Muslim/3rd Quarter Required Data/QPR/Shafi Muhammad Goth/H. Staff Attendance/Staff Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\Staff Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\3rd Quarter Required Data\QPR\Shafi Muhammad Goth\H. Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0B1238-4E95-42BD-BA91-4047F174BE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B25D9E4-ABCD-4E50-933E-BAFDFA6A44A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST-2024" sheetId="7" r:id="rId1"/>
@@ -18,6 +18,11 @@
     <sheet name="OCTOBER-2024" sheetId="13" r:id="rId3"/>
     <sheet name="NOVEMBER-2024" sheetId="14" r:id="rId4"/>
     <sheet name="DECEMBER-2024" sheetId="15" r:id="rId5"/>
+    <sheet name="JANUARY-2025" sheetId="16" r:id="rId6"/>
+    <sheet name="FEBRUARY-2025" sheetId="17" r:id="rId7"/>
+    <sheet name="MARCH-2025" sheetId="18" r:id="rId8"/>
+    <sheet name="APRIL-2025" sheetId="21" r:id="rId9"/>
+    <sheet name="MAY-2025" sheetId="22" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="36">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -117,6 +122,36 @@
   <si>
     <t>WINTER VICATIONS</t>
   </si>
+  <si>
+    <t>Kashmir Day</t>
+  </si>
+  <si>
+    <t>Shab-E-Baraat</t>
+  </si>
+  <si>
+    <t>Urs Lal Shehbaz Qalandar</t>
+  </si>
+  <si>
+    <t>Ahsan Ali</t>
+  </si>
+  <si>
+    <t>Youm-E-Ali</t>
+  </si>
+  <si>
+    <t>Laylat al-Qadr</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Eid Ul Fitar</t>
+  </si>
+  <si>
+    <t>Death Anniversory (SZAB)</t>
+  </si>
+  <si>
+    <t>Labour Day</t>
+  </si>
 </sst>
 </file>
 
@@ -166,7 +201,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,8 +232,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -378,11 +425,161 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -420,18 +617,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -454,6 +639,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -465,11 +662,428 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="56">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -582,11 +1196,91 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -912,54 +1606,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="15"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="10" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Thu</v>
@@ -1084,13 +1778,13 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AI3" s="22" t="s">
+      <c r="AI3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="23"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1230,7 +1924,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -1251,7 +1945,7 @@
       <c r="M5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -1272,13 +1966,13 @@
       <c r="T5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="V5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="20" t="s">
         <v>15</v>
       </c>
       <c r="X5" s="4" t="s">
@@ -1293,10 +1987,10 @@
       <c r="AA5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB5" s="13" t="s">
+      <c r="AB5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AC5" s="22" t="s">
         <v>11</v>
       </c>
       <c r="AD5" s="4" t="s">
@@ -1308,7 +2002,7 @@
       <c r="AF5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG5" s="15" t="s">
+      <c r="AG5" s="22" t="s">
         <v>16</v>
       </c>
       <c r="AH5" s="4" t="s">
@@ -1347,14 +2041,14 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="13"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="13"/>
+      <c r="N6" s="20"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
@@ -1369,11 +2063,11 @@
       <c r="T6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="13"/>
+      <c r="U6" s="20"/>
       <c r="V6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="13"/>
+      <c r="W6" s="20"/>
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1386,8 +2080,8 @@
       <c r="AA6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="15"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="22"/>
       <c r="AD6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1397,7 +2091,7 @@
       <c r="AF6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="15"/>
+      <c r="AG6" s="22"/>
       <c r="AH6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1435,14 +2129,14 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="13"/>
+      <c r="N7" s="20"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4" t="s">
@@ -1457,11 +2151,11 @@
       <c r="T7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U7" s="13"/>
+      <c r="U7" s="20"/>
       <c r="V7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="13"/>
+      <c r="W7" s="20"/>
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1474,8 +2168,8 @@
       <c r="AA7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="15"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="22"/>
       <c r="AD7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1485,7 +2179,7 @@
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="15"/>
+      <c r="AG7" s="22"/>
       <c r="AH7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1523,14 +2217,14 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="13"/>
+      <c r="G8" s="20"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="13"/>
+      <c r="N8" s="20"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
@@ -1545,11 +2239,11 @@
       <c r="T8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U8" s="13"/>
+      <c r="U8" s="20"/>
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="13"/>
+      <c r="W8" s="20"/>
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1562,8 +2256,8 @@
       <c r="AA8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="15"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="22"/>
       <c r="AD8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1573,7 +2267,7 @@
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG8" s="15"/>
+      <c r="AG8" s="22"/>
       <c r="AH8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1611,14 +2305,14 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="13"/>
+      <c r="N9" s="20"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
@@ -1633,11 +2327,11 @@
       <c r="T9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U9" s="13"/>
+      <c r="U9" s="20"/>
       <c r="V9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W9" s="13"/>
+      <c r="W9" s="20"/>
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1650,8 +2344,8 @@
       <c r="AA9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="15"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="22"/>
       <c r="AD9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1661,7 +2355,7 @@
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG9" s="15"/>
+      <c r="AG9" s="22"/>
       <c r="AH9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1699,14 +2393,14 @@
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="14"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="14"/>
+      <c r="N10" s="21"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6" t="s">
@@ -1721,11 +2415,11 @@
       <c r="T10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U10" s="14"/>
+      <c r="U10" s="21"/>
       <c r="V10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="14"/>
+      <c r="W10" s="21"/>
       <c r="X10" s="6" t="s">
         <v>6</v>
       </c>
@@ -1738,8 +2432,8 @@
       <c r="AA10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="16"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="23"/>
       <c r="AD10" s="6" t="s">
         <v>6</v>
       </c>
@@ -1749,7 +2443,7 @@
       <c r="AF10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG10" s="16"/>
+      <c r="AG10" s="23"/>
       <c r="AH10" s="6" t="s">
         <v>6</v>
       </c>
@@ -1787,16 +2481,796 @@
     <mergeCell ref="AC5:AC10"/>
     <mergeCell ref="AG5:AG10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:AH4 G5 N5 U5 W5 AB5:AC5 AG5 D5:F10 H5:M10 V5:V10 AD5:AF10 AH5:AH10 X5:AA10 O5:T10">
-    <cfRule type="expression" dxfId="14" priority="97">
+  <conditionalFormatting sqref="D3:AH4 G5 N5 U5 W5 AB5:AC5 AG5 D5:F10 H5:M10 O5:T10 V5:V10 X5:AA10 AD5:AF10 AH5:AH10">
+    <cfRule type="expression" dxfId="55" priority="97">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5 N5 U5 W5 AB5:AC5 AG5 D5:F10 H5:M10 V5:V10 AD5:AF10 AH5:AH10 X5:AA10 O5:T10">
-    <cfRule type="cellIs" dxfId="13" priority="98" operator="equal">
+  <conditionalFormatting sqref="G5 N5 U5 W5 AB5:AC5 AG5 D5:F10 H5:M10 O5:T10 V5:V10 X5:AA10 AD5:AF10 AH5:AH10">
+    <cfRule type="cellIs" dxfId="54" priority="98" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="99" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A4AFE2-8E45-43DC-BC24-3B2144E6E59A}">
+  <dimension ref="A1:X18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="19" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="5.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="15"/>
+    </row>
+    <row r="3" spans="1:24" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45" t="str">
+        <f>TEXT(D4,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="E3" s="46" t="str">
+        <f t="shared" ref="E3:S3" si="0">TEXT(E4,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="F3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="G3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="H3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="I3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="J3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="K3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="L3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="M3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="N3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="O3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="P3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="Q3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="R3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="S3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="T3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="50"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="28">
+        <v>45778</v>
+      </c>
+      <c r="E4" s="28">
+        <v>45779</v>
+      </c>
+      <c r="F4" s="28">
+        <v>45780</v>
+      </c>
+      <c r="G4" s="28">
+        <v>45781</v>
+      </c>
+      <c r="H4" s="28">
+        <v>45782</v>
+      </c>
+      <c r="I4" s="28">
+        <v>45783</v>
+      </c>
+      <c r="J4" s="28">
+        <v>45784</v>
+      </c>
+      <c r="K4" s="28">
+        <v>45785</v>
+      </c>
+      <c r="L4" s="28">
+        <v>45786</v>
+      </c>
+      <c r="M4" s="28">
+        <v>45787</v>
+      </c>
+      <c r="N4" s="28">
+        <v>45788</v>
+      </c>
+      <c r="O4" s="28">
+        <v>45789</v>
+      </c>
+      <c r="P4" s="28">
+        <v>45790</v>
+      </c>
+      <c r="Q4" s="28">
+        <v>45791</v>
+      </c>
+      <c r="R4" s="28">
+        <v>45792</v>
+      </c>
+      <c r="S4" s="28">
+        <v>45793</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="3">
+        <f>COUNTIF(D5:S5,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="U5" s="4">
+        <f>COUNTIF(D5:S5,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <f>COUNTIF(D5:S5,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <v>5</v>
+      </c>
+      <c r="X5" s="11">
+        <f>T5+V5+W5</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="3">
+        <f>COUNTIF(D6:S6,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="U6" s="4">
+        <f>COUNTIF(D6:S6,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <f>COUNTIF(D6:S6,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="W6" s="4">
+        <f>COUNTBLANK(D6:S6)</f>
+        <v>3</v>
+      </c>
+      <c r="X6" s="11">
+        <f t="shared" ref="X6:X11" si="1">T6+V6+W6</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="20"/>
+      <c r="O7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="3">
+        <f>COUNTIF(D7:S7,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="U7" s="4">
+        <f>COUNTIF(D7:S7,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <f>COUNTIF(D7:S7,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="W7" s="4">
+        <f>COUNTBLANK(D7:S7)</f>
+        <v>3</v>
+      </c>
+      <c r="X7" s="11">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="55"/>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="20"/>
+      <c r="O8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="3">
+        <f>COUNTIF(D8:S8,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="4">
+        <f>COUNTIF(D8:S8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <f>COUNTIF(D8:S8,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="4">
+        <f>COUNTBLANK(D8:S8)</f>
+        <v>3</v>
+      </c>
+      <c r="X8" s="11">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="20"/>
+      <c r="O9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="3">
+        <f>COUNTIF(D9:S9,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="U9" s="4">
+        <f>COUNTIF(D9:S9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <f>COUNTIF(D9:S9,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="4">
+        <f>COUNTBLANK(D9:S9)</f>
+        <v>3</v>
+      </c>
+      <c r="X9" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="20"/>
+      <c r="O10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" s="3">
+        <f>COUNTIF(D10:S10,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="U10" s="4">
+        <f>COUNTIF(D10:S10,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <f>COUNTIF(D10:S10,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="W10" s="4">
+        <f>COUNTBLANK(D10:S10)</f>
+        <v>3</v>
+      </c>
+      <c r="X10" s="11">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="56"/>
+      <c r="E11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="21"/>
+      <c r="O11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="5">
+        <f>COUNTIF(D11:S11,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="U11" s="6">
+        <f>COUNTIF(D11:S11,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="6">
+        <f>COUNTIF(D11:S11,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="W11" s="6">
+        <f>COUNTBLANK(D11:S11)</f>
+        <v>3</v>
+      </c>
+      <c r="X11" s="12">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="N5:N11"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="T3:X3"/>
+    <mergeCell ref="D5:D11"/>
+    <mergeCell ref="G5:G11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F5:F11 N5 H5:M11 O5:S11">
+    <cfRule type="cellIs" dxfId="12" priority="27" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="28" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11 N5 H5:M11 D3:S4 O5:S11">
+    <cfRule type="expression" dxfId="10" priority="26">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>G$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E11">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E11">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D11">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1820,53 +3294,53 @@
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:38" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="15"/>
     </row>
     <row r="3" spans="1:38" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="10" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sun</v>
@@ -1987,13 +3461,13 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AH3" s="22" t="s">
+      <c r="AH3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="23"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="19"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2121,7 +3595,7 @@
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -2142,7 +3616,7 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -2163,7 +3637,7 @@
       <c r="Q5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="S5" s="4" t="s">
@@ -2184,7 +3658,7 @@
       <c r="X5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="Z5" s="4" t="s">
@@ -2205,22 +3679,22 @@
       <c r="AE5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF5" s="13" t="s">
+      <c r="AF5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="AG5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AH5" s="4">
-        <f>COUNTIF(D5:AG5,"P")</f>
+        <f t="shared" ref="AH5:AH10" si="1">COUNTIF(D5:AG5,"P")</f>
         <v>24</v>
       </c>
       <c r="AI5" s="4">
-        <f>COUNTIF(D5:AG5,"A")</f>
+        <f t="shared" ref="AI5:AI10" si="2">COUNTIF(D5:AG5,"A")</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="4">
-        <f>COUNTIF(D5:AG5,"L")</f>
+        <f t="shared" ref="AJ5:AJ10" si="3">COUNTIF(D5:AG5,"L")</f>
         <v>0</v>
       </c>
       <c r="AK5" s="4">
@@ -2241,7 +3715,7 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2260,7 +3734,7 @@
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="13"/>
+      <c r="K6" s="20"/>
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2279,7 +3753,7 @@
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="13"/>
+      <c r="R6" s="20"/>
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2296,7 +3770,7 @@
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="13"/>
+      <c r="Y6" s="20"/>
       <c r="Z6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2315,20 +3789,20 @@
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF6" s="13"/>
+      <c r="AF6" s="20"/>
       <c r="AG6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AH6" s="4">
-        <f>COUNTIF(D6:AG6,"P")</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="AI6" s="4">
-        <f>COUNTIF(D6:AG6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="4">
-        <f>COUNTIF(D6:AG6,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK6" s="4">
@@ -2336,7 +3810,7 @@
         <v>6</v>
       </c>
       <c r="AL6" s="11">
-        <f t="shared" ref="AL6:AL10" si="1">AH6+AJ6+AK6</f>
+        <f t="shared" ref="AL6:AL10" si="4">AH6+AJ6+AK6</f>
         <v>30</v>
       </c>
     </row>
@@ -2350,7 +3824,7 @@
       <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2369,7 +3843,7 @@
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="13"/>
+      <c r="K7" s="20"/>
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2388,7 +3862,7 @@
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R7" s="13"/>
+      <c r="R7" s="20"/>
       <c r="S7" s="4" t="s">
         <v>7</v>
       </c>
@@ -2405,7 +3879,7 @@
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y7" s="13"/>
+      <c r="Y7" s="20"/>
       <c r="Z7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2424,20 +3898,20 @@
       <c r="AE7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF7" s="13"/>
+      <c r="AF7" s="20"/>
       <c r="AG7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AH7" s="4">
-        <f>COUNTIF(D7:AG7,"P")</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="AI7" s="4">
-        <f>COUNTIF(D7:AG7,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ7" s="4">
-        <f>COUNTIF(D7:AG7,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK7" s="4">
@@ -2445,7 +3919,7 @@
         <v>6</v>
       </c>
       <c r="AL7" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -2459,7 +3933,7 @@
       <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2478,7 +3952,7 @@
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="13"/>
+      <c r="K8" s="20"/>
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2497,7 +3971,7 @@
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="13"/>
+      <c r="R8" s="20"/>
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2514,7 +3988,7 @@
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="13"/>
+      <c r="Y8" s="20"/>
       <c r="Z8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2533,20 +4007,20 @@
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF8" s="13"/>
+      <c r="AF8" s="20"/>
       <c r="AG8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AH8" s="4">
-        <f>COUNTIF(D8:AG8,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AI8" s="4">
-        <f>COUNTIF(D8:AG8,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ8" s="4">
-        <f>COUNTIF(D8:AG8,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK8" s="4">
@@ -2554,7 +4028,7 @@
         <v>6</v>
       </c>
       <c r="AL8" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
@@ -2568,7 +4042,7 @@
       <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2587,7 +4061,7 @@
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="13"/>
+      <c r="K9" s="20"/>
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2606,7 +4080,7 @@
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="13"/>
+      <c r="R9" s="20"/>
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2623,7 +4097,7 @@
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y9" s="13"/>
+      <c r="Y9" s="20"/>
       <c r="Z9" s="4" t="s">
         <v>7</v>
       </c>
@@ -2642,20 +4116,20 @@
       <c r="AE9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF9" s="13"/>
+      <c r="AF9" s="20"/>
       <c r="AG9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AH9" s="4">
-        <f>COUNTIF(D9:AG9,"P")</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="AI9" s="4">
-        <f>COUNTIF(D9:AG9,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ9" s="4">
-        <f>COUNTIF(D9:AG9,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK9" s="4">
@@ -2663,7 +4137,7 @@
         <v>6</v>
       </c>
       <c r="AL9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -2677,7 +4151,7 @@
       <c r="C10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="6" t="s">
         <v>6</v>
       </c>
@@ -2696,7 +4170,7 @@
       <c r="J10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="14"/>
+      <c r="K10" s="21"/>
       <c r="L10" s="6" t="s">
         <v>6</v>
       </c>
@@ -2715,7 +4189,7 @@
       <c r="Q10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="R10" s="14"/>
+      <c r="R10" s="21"/>
       <c r="S10" s="6" t="s">
         <v>6</v>
       </c>
@@ -2732,7 +4206,7 @@
       <c r="X10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Y10" s="14"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="6" t="s">
         <v>6</v>
       </c>
@@ -2751,20 +4225,20 @@
       <c r="AE10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AF10" s="14"/>
+      <c r="AF10" s="21"/>
       <c r="AG10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="AH10" s="6">
-        <f>COUNTIF(D10:AG10,"P")</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="AI10" s="6">
-        <f>COUNTIF(D10:AG10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ10" s="6">
-        <f>COUNTIF(D10:AG10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK10" s="6">
@@ -2772,7 +4246,7 @@
         <v>6</v>
       </c>
       <c r="AL10" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
@@ -2789,17 +4263,17 @@
     <mergeCell ref="AF5:AF10"/>
     <mergeCell ref="T5:T10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5 K5 R5 Y5 AF5 E5:J10 L5:Q10 S5:S10 Z5:AE10 U5:X10 T5 D3:AG4 AG5:AG10">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>D$3="SUN"</formula>
+  <conditionalFormatting sqref="D5 K5 R5 T5 Y5 AF5 E5:J10 L5:Q10 S5:S10 U5:X10 Z5:AE10 AG5:AG10">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5 K5 R5 Y5 AF5 E5:J10 L5:Q10 S5:S10 Z5:AE10 AG5:AG10 U5:X10 T5">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>"P"</formula>
+  <conditionalFormatting sqref="D3:AG4 D5 K5 R5 T5 Y5 AF5 E5:J10 L5:Q10 S5:S10 U5:X10 Z5:AE10 AG5:AG10">
+    <cfRule type="expression" dxfId="50" priority="1">
+      <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2823,54 +4297,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="15"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="10" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -2995,13 +4469,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="22" t="s">
+      <c r="AI3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="23"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3147,7 +4621,7 @@
       <c r="H5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -3168,7 +4642,7 @@
       <c r="O5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -3189,7 +4663,7 @@
       <c r="V5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="X5" s="4" t="s">
@@ -3210,7 +4684,7 @@
       <c r="AC5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD5" s="13" t="s">
+      <c r="AD5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="AE5" s="4" t="s">
@@ -3270,7 +4744,7 @@
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="13"/>
+      <c r="I6" s="20"/>
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3289,7 +4763,7 @@
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="20"/>
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3308,7 +4782,7 @@
       <c r="V6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="13"/>
+      <c r="W6" s="20"/>
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3327,7 +4801,7 @@
       <c r="AC6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD6" s="13"/>
+      <c r="AD6" s="20"/>
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3386,7 +4860,7 @@
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="13"/>
+      <c r="I7" s="20"/>
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3405,7 +4879,7 @@
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="13"/>
+      <c r="P7" s="20"/>
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3424,7 +4898,7 @@
       <c r="V7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="13"/>
+      <c r="W7" s="20"/>
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3443,7 +4917,7 @@
       <c r="AC7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD7" s="13"/>
+      <c r="AD7" s="20"/>
       <c r="AE7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3502,7 +4976,7 @@
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="13"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3521,7 +4995,7 @@
       <c r="O8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="20"/>
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3540,7 +5014,7 @@
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="13"/>
+      <c r="W8" s="20"/>
       <c r="X8" s="4" t="s">
         <v>7</v>
       </c>
@@ -3559,7 +5033,7 @@
       <c r="AC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD8" s="13"/>
+      <c r="AD8" s="20"/>
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3618,7 +5092,7 @@
       <c r="H9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="13"/>
+      <c r="I9" s="20"/>
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3637,7 +5111,7 @@
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="20"/>
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3656,7 +5130,7 @@
       <c r="V9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W9" s="13"/>
+      <c r="W9" s="20"/>
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3675,7 +5149,7 @@
       <c r="AC9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="13"/>
+      <c r="AD9" s="20"/>
       <c r="AE9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3734,7 +5208,7 @@
       <c r="H10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="I10" s="21"/>
       <c r="J10" s="6" t="s">
         <v>6</v>
       </c>
@@ -3753,7 +5227,7 @@
       <c r="O10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="14"/>
+      <c r="P10" s="21"/>
       <c r="Q10" s="6" t="s">
         <v>6</v>
       </c>
@@ -3772,7 +5246,7 @@
       <c r="V10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="14"/>
+      <c r="W10" s="21"/>
       <c r="X10" s="6" t="s">
         <v>7</v>
       </c>
@@ -3791,7 +5265,7 @@
       <c r="AC10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD10" s="14"/>
+      <c r="AD10" s="21"/>
       <c r="AE10" s="6" t="s">
         <v>6</v>
       </c>
@@ -3836,16 +5310,16 @@
     <mergeCell ref="AI3:AM3"/>
     <mergeCell ref="I5:I10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:AH4 I5 P5 W5 AD5 Q5:V10 X5:AC10 D5:H10 AE5:AH10 J5:O10">
-    <cfRule type="expression" dxfId="8" priority="1">
+  <conditionalFormatting sqref="D3:AH4 I5 P5 W5 AD5 D5:H10 J5:O10 Q5:V10 X5:AC10 AE5:AH10">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5 P5 W5 AD5 Q5:V10 X5:AC10 D5:H10 AE5:AH10 J5:O10">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+  <conditionalFormatting sqref="I5 P5 W5 AD5 D5:H10 J5:O10 Q5:V10 X5:AC10 AE5:AH10">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3869,53 +5343,53 @@
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:38" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="15"/>
     </row>
     <row r="3" spans="1:38" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="10" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Fri</v>
@@ -4036,13 +5510,13 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AH3" s="22" t="s">
+      <c r="AH3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="23"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="19"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4176,7 +5650,7 @@
       <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -4197,7 +5671,7 @@
       <c r="L5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="4" t="s">
@@ -4218,7 +5692,7 @@
       <c r="S5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="U5" s="4" t="s">
@@ -4239,7 +5713,7 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AA5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="AB5" s="4" t="s">
@@ -4261,15 +5735,15 @@
         <v>6</v>
       </c>
       <c r="AH5" s="4">
-        <f>COUNTIF(D5:AG5,"P")</f>
+        <f t="shared" ref="AH5:AH10" si="1">COUNTIF(D5:AG5,"P")</f>
         <v>26</v>
       </c>
       <c r="AI5" s="4">
-        <f>COUNTIF(D5:AG5,"A")</f>
+        <f t="shared" ref="AI5:AI10" si="2">COUNTIF(D5:AG5,"A")</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="4">
-        <f>COUNTIF(D5:AG5,"L")</f>
+        <f t="shared" ref="AJ5:AJ10" si="3">COUNTIF(D5:AG5,"L")</f>
         <v>0</v>
       </c>
       <c r="AK5" s="4">
@@ -4296,7 +5770,7 @@
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="20"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4315,7 +5789,7 @@
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="13"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4334,7 +5808,7 @@
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="13"/>
+      <c r="T6" s="20"/>
       <c r="U6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4353,7 +5827,7 @@
       <c r="Z6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA6" s="13"/>
+      <c r="AA6" s="20"/>
       <c r="AB6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4373,15 +5847,15 @@
         <v>6</v>
       </c>
       <c r="AH6" s="4">
-        <f>COUNTIF(D6:AG6,"P")</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="AI6" s="4">
-        <f>COUNTIF(D6:AG6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="4">
-        <f>COUNTIF(D6:AG6,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK6" s="4">
@@ -4389,7 +5863,7 @@
         <v>4</v>
       </c>
       <c r="AL6" s="11">
-        <f t="shared" ref="AL6:AL10" si="1">AH6+AJ6+AK6</f>
+        <f t="shared" ref="AL6:AL10" si="4">AH6+AJ6+AK6</f>
         <v>30</v>
       </c>
     </row>
@@ -4409,7 +5883,7 @@
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="20"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4428,7 +5902,7 @@
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="20"/>
       <c r="N7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4447,7 +5921,7 @@
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="13"/>
+      <c r="T7" s="20"/>
       <c r="U7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4466,7 +5940,7 @@
       <c r="Z7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA7" s="13"/>
+      <c r="AA7" s="20"/>
       <c r="AB7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4486,15 +5960,15 @@
         <v>7</v>
       </c>
       <c r="AH7" s="4">
-        <f>COUNTIF(D7:AG7,"P")</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="AI7" s="4">
-        <f>COUNTIF(D7:AG7,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ7" s="4">
-        <f>COUNTIF(D7:AG7,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK7" s="4">
@@ -4502,7 +5976,7 @@
         <v>4</v>
       </c>
       <c r="AL7" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -4522,7 +5996,7 @@
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4541,7 +6015,7 @@
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="13"/>
+      <c r="M8" s="20"/>
       <c r="N8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4560,7 +6034,7 @@
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T8" s="13"/>
+      <c r="T8" s="20"/>
       <c r="U8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4579,7 +6053,7 @@
       <c r="Z8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA8" s="13"/>
+      <c r="AA8" s="20"/>
       <c r="AB8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4599,15 +6073,15 @@
         <v>6</v>
       </c>
       <c r="AH8" s="4">
-        <f>COUNTIF(D8:AG8,"P")</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="AI8" s="4">
-        <f>COUNTIF(D8:AG8,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ8" s="4">
-        <f>COUNTIF(D8:AG8,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK8" s="4">
@@ -4615,7 +6089,7 @@
         <v>4</v>
       </c>
       <c r="AL8" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -4635,7 +6109,7 @@
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="20"/>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4654,7 +6128,7 @@
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="13"/>
+      <c r="M9" s="20"/>
       <c r="N9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4673,7 +6147,7 @@
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="13"/>
+      <c r="T9" s="20"/>
       <c r="U9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4692,7 +6166,7 @@
       <c r="Z9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AA9" s="13"/>
+      <c r="AA9" s="20"/>
       <c r="AB9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4712,15 +6186,15 @@
         <v>7</v>
       </c>
       <c r="AH9" s="4">
-        <f>COUNTIF(D9:AG9,"P")</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="AI9" s="4">
-        <f>COUNTIF(D9:AG9,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ9" s="4">
-        <f>COUNTIF(D9:AG9,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK9" s="4">
@@ -4728,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="AL9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
@@ -4748,7 +6222,7 @@
       <c r="E10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="6" t="s">
         <v>6</v>
       </c>
@@ -4767,7 +6241,7 @@
       <c r="L10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="14"/>
+      <c r="M10" s="21"/>
       <c r="N10" s="6" t="s">
         <v>6</v>
       </c>
@@ -4786,7 +6260,7 @@
       <c r="S10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="14"/>
+      <c r="T10" s="21"/>
       <c r="U10" s="6" t="s">
         <v>6</v>
       </c>
@@ -4805,7 +6279,7 @@
       <c r="Z10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AA10" s="14"/>
+      <c r="AA10" s="21"/>
       <c r="AB10" s="6" t="s">
         <v>6</v>
       </c>
@@ -4825,15 +6299,15 @@
         <v>7</v>
       </c>
       <c r="AH10" s="6">
-        <f>COUNTIF(D10:AG10,"P")</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="AI10" s="6">
-        <f>COUNTIF(D10:AG10,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ10" s="6">
-        <f>COUNTIF(D10:AG10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK10" s="6">
@@ -4841,7 +6315,7 @@
         <v>4</v>
       </c>
       <c r="AL10" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -4856,16 +6330,16 @@
     <mergeCell ref="M5:M10"/>
     <mergeCell ref="T5:T10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:E10 F5 M5 T5 AA5 G5:L10 N5:S10 U5:Z10 AB5:AG10 D3:AG4">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="D3:AG4 F5 M5 T5 AA5 D5:E10 G5:L10 N5:S10 U5:Z10 AB5:AG10">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:E10 F5 M5 T5 AA5 G5:L10 N5:S10 U5:Z10 AB5:AG10">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+  <conditionalFormatting sqref="F5 M5 T5 AA5 D5:E10 G5:L10 N5:S10 U5:Z10 AB5:AG10">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4890,54 +6364,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="15"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="10" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sun</v>
@@ -5062,13 +6536,13 @@
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AI3" s="22" t="s">
+      <c r="AI3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="23"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -5199,7 +6673,7 @@
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -5220,7 +6694,7 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -5241,7 +6715,7 @@
       <c r="Q5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="S5" s="4" t="s">
@@ -5262,7 +6736,7 @@
       <c r="X5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="Z5" s="26" t="s">
@@ -5283,7 +6757,7 @@
       <c r="AE5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AF5" s="13" t="s">
+      <c r="AF5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="AG5" s="26" t="s">
@@ -5322,7 +6796,7 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5341,7 +6815,7 @@
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="13"/>
+      <c r="K6" s="20"/>
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5360,7 +6834,7 @@
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="13"/>
+      <c r="R6" s="20"/>
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5377,14 +6851,14 @@
         <v>6</v>
       </c>
       <c r="X6" s="26"/>
-      <c r="Y6" s="13"/>
+      <c r="Y6" s="20"/>
       <c r="Z6" s="26"/>
       <c r="AA6" s="26"/>
       <c r="AB6" s="26"/>
       <c r="AC6" s="26"/>
       <c r="AD6" s="26"/>
       <c r="AE6" s="26"/>
-      <c r="AF6" s="13"/>
+      <c r="AF6" s="20"/>
       <c r="AG6" s="26"/>
       <c r="AH6" s="26"/>
       <c r="AI6" s="4">
@@ -5418,7 +6892,7 @@
       <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5437,7 +6911,7 @@
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="13"/>
+      <c r="K7" s="20"/>
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5456,7 +6930,7 @@
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R7" s="13"/>
+      <c r="R7" s="20"/>
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5473,14 +6947,14 @@
         <v>6</v>
       </c>
       <c r="X7" s="26"/>
-      <c r="Y7" s="13"/>
+      <c r="Y7" s="20"/>
       <c r="Z7" s="26"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="26"/>
       <c r="AC7" s="26"/>
       <c r="AD7" s="26"/>
       <c r="AE7" s="26"/>
-      <c r="AF7" s="13"/>
+      <c r="AF7" s="20"/>
       <c r="AG7" s="26"/>
       <c r="AH7" s="26"/>
       <c r="AI7" s="4">
@@ -5514,7 +6988,7 @@
       <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5533,7 +7007,7 @@
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="13"/>
+      <c r="K8" s="20"/>
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +7026,7 @@
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="13"/>
+      <c r="R8" s="20"/>
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5569,14 +7043,14 @@
         <v>6</v>
       </c>
       <c r="X8" s="26"/>
-      <c r="Y8" s="13"/>
+      <c r="Y8" s="20"/>
       <c r="Z8" s="26"/>
       <c r="AA8" s="26"/>
       <c r="AB8" s="26"/>
       <c r="AC8" s="26"/>
       <c r="AD8" s="26"/>
       <c r="AE8" s="26"/>
-      <c r="AF8" s="13"/>
+      <c r="AF8" s="20"/>
       <c r="AG8" s="26"/>
       <c r="AH8" s="26"/>
       <c r="AI8" s="4">
@@ -5610,7 +7084,7 @@
       <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5629,7 +7103,7 @@
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="13"/>
+      <c r="K9" s="20"/>
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5648,7 +7122,7 @@
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="13"/>
+      <c r="R9" s="20"/>
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5665,14 +7139,14 @@
         <v>6</v>
       </c>
       <c r="X9" s="26"/>
-      <c r="Y9" s="13"/>
+      <c r="Y9" s="20"/>
       <c r="Z9" s="26"/>
       <c r="AA9" s="26"/>
       <c r="AB9" s="26"/>
       <c r="AC9" s="26"/>
       <c r="AD9" s="26"/>
       <c r="AE9" s="26"/>
-      <c r="AF9" s="13"/>
+      <c r="AF9" s="20"/>
       <c r="AG9" s="26"/>
       <c r="AH9" s="26"/>
       <c r="AI9" s="4">
@@ -5706,7 +7180,7 @@
       <c r="C10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="6" t="s">
         <v>6</v>
       </c>
@@ -5725,7 +7199,7 @@
       <c r="J10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="14"/>
+      <c r="K10" s="21"/>
       <c r="L10" s="6" t="s">
         <v>6</v>
       </c>
@@ -5744,7 +7218,7 @@
       <c r="Q10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="R10" s="14"/>
+      <c r="R10" s="21"/>
       <c r="S10" s="6" t="s">
         <v>6</v>
       </c>
@@ -5761,14 +7235,14 @@
         <v>6</v>
       </c>
       <c r="X10" s="27"/>
-      <c r="Y10" s="14"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="27"/>
       <c r="AA10" s="27"/>
       <c r="AB10" s="27"/>
       <c r="AC10" s="27"/>
       <c r="AD10" s="27"/>
       <c r="AE10" s="27"/>
-      <c r="AF10" s="14"/>
+      <c r="AF10" s="21"/>
       <c r="AG10" s="27"/>
       <c r="AH10" s="27"/>
       <c r="AI10" s="6">
@@ -5795,6 +7269,13 @@
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AI3:AM3"/>
+    <mergeCell ref="AA5:AA10"/>
+    <mergeCell ref="AH5:AH10"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="K5:K10"/>
     <mergeCell ref="AG5:AG10"/>
     <mergeCell ref="R5:R10"/>
     <mergeCell ref="Y5:Y10"/>
@@ -5805,24 +7286,4288 @@
     <mergeCell ref="AC5:AC10"/>
     <mergeCell ref="AD5:AD10"/>
     <mergeCell ref="AE5:AE10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5 K5 R5 X5:AH5 E5:J10 L5:Q10 S5:W10">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:AH4 D5 K5 R5 X5:AH5 E5:J10 L5:Q10 S5:W10">
+    <cfRule type="expression" dxfId="41" priority="1">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0236B8F2-5EB7-4933-8650-B450A3EE0A5D}">
+  <dimension ref="A1:AM17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="33" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="3.7109375" customWidth="1"/>
+    <col min="35" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="15"/>
+    </row>
+    <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="10" t="str">
+        <f>TEXT(D4,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="E3" s="10" t="str">
+        <f t="shared" ref="E3:AH3" si="0">TEXT(E4,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="F3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="H3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="I3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="K3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="L3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="M3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="N3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="O3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="P3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="Q3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="R3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="S3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="T3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="U3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="V3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="W3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="X3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="Y3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="Z3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AA3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AB3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="AC3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AD3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AE3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="AF3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AG3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AH3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AI3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7">
+        <v>45658</v>
+      </c>
+      <c r="E4" s="7">
+        <v>45659</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45660</v>
+      </c>
+      <c r="G4" s="7">
+        <v>45661</v>
+      </c>
+      <c r="H4" s="7">
+        <v>45662</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45663</v>
+      </c>
+      <c r="J4" s="7">
+        <v>45664</v>
+      </c>
+      <c r="K4" s="7">
+        <v>45665</v>
+      </c>
+      <c r="L4" s="7">
+        <v>45666</v>
+      </c>
+      <c r="M4" s="7">
+        <v>45667</v>
+      </c>
+      <c r="N4" s="7">
+        <v>45668</v>
+      </c>
+      <c r="O4" s="7">
+        <v>45669</v>
+      </c>
+      <c r="P4" s="7">
+        <v>45670</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>45671</v>
+      </c>
+      <c r="R4" s="7">
+        <v>45672</v>
+      </c>
+      <c r="S4" s="7">
+        <v>45673</v>
+      </c>
+      <c r="T4" s="7">
+        <v>45674</v>
+      </c>
+      <c r="U4" s="7">
+        <v>45675</v>
+      </c>
+      <c r="V4" s="7">
+        <v>45676</v>
+      </c>
+      <c r="W4" s="7">
+        <v>45677</v>
+      </c>
+      <c r="X4" s="7">
+        <v>45678</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>45679</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>45680</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>45681</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>45682</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>45683</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>45684</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>45685</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>45686</v>
+      </c>
+      <c r="AG4" s="7">
+        <v>45687</v>
+      </c>
+      <c r="AH4" s="7">
+        <v>45688</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" ref="AI5:AI10" si="1">COUNTIF(D5:AH5,"P")</f>
+        <v>27</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" ref="AJ5:AJ10" si="2">COUNTIF(D5:AH5,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" ref="AK5:AK10" si="3">COUNTIF(D5:AH5,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="11">
+        <f>AI5+AK5+AL5</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="20"/>
+      <c r="W6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" ref="AL6:AL10" si="4">COUNTBLANK(D6:AH6)</f>
+        <v>4</v>
+      </c>
+      <c r="AM6" s="11">
+        <f t="shared" ref="AM6:AM10" si="5">AI6+AK6+AL6</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="20"/>
+      <c r="W7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AM7" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" s="20"/>
+      <c r="W8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AM8" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="20"/>
+      <c r="P9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="20"/>
+      <c r="W9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AJ9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AM9" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="21"/>
+      <c r="P10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="21"/>
+      <c r="W10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="21"/>
+      <c r="AD10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI10" s="6">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AJ10" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK10" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="6">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AM10" s="12">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H5:H10"/>
+    <mergeCell ref="O5:O10"/>
+    <mergeCell ref="V5:V10"/>
+    <mergeCell ref="AC5:AC10"/>
     <mergeCell ref="A2:AM2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="AI3:AM3"/>
-    <mergeCell ref="AA5:AA10"/>
-    <mergeCell ref="AH5:AH10"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="K5:K10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:AH4 D5 K5 R5 E5:J10 L5:Q10 S5:W10 X5:AH5">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="H5 O5 V5 AC5 D5:G10 I5:N10 P5:U10 W5:AB10 AD5:AH10">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:AH4 H5 O5 V5 AC5 D5:G10 I5:N10 P5:U10 W5:AB10 AD5:AH10">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5 K5 R5 E5:J10 L5:Q10 S5:W10 X5:AH5">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2278BB08-A46D-40A6-8C4D-472E092480D2}">
+  <dimension ref="A1:AJ17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="31" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="5.7109375" customWidth="1"/>
+    <col min="36" max="36" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:36" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="15"/>
+    </row>
+    <row r="3" spans="1:36" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="10" t="str">
+        <f>TEXT(D4,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="E3" s="10" t="str">
+        <f t="shared" ref="E3:AE3" si="0">TEXT(E4,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="F3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="H3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="I3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="K3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="L3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="M3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="N3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="O3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="P3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="R3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="S3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="T3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="U3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="V3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="W3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="X3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="Y3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="Z3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AA3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AB3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="AC3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AD3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AE3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AF3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="19"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7">
+        <v>45689</v>
+      </c>
+      <c r="E4" s="7">
+        <v>45690</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45691</v>
+      </c>
+      <c r="G4" s="7">
+        <v>45692</v>
+      </c>
+      <c r="H4" s="7">
+        <v>45693</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45694</v>
+      </c>
+      <c r="J4" s="7">
+        <v>45695</v>
+      </c>
+      <c r="K4" s="7">
+        <v>45696</v>
+      </c>
+      <c r="L4" s="7">
+        <v>45697</v>
+      </c>
+      <c r="M4" s="7">
+        <v>45698</v>
+      </c>
+      <c r="N4" s="7">
+        <v>45699</v>
+      </c>
+      <c r="O4" s="7">
+        <v>45700</v>
+      </c>
+      <c r="P4" s="7">
+        <v>45701</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>45702</v>
+      </c>
+      <c r="R4" s="7">
+        <v>45703</v>
+      </c>
+      <c r="S4" s="7">
+        <v>45704</v>
+      </c>
+      <c r="T4" s="7">
+        <v>45705</v>
+      </c>
+      <c r="U4" s="7">
+        <v>45706</v>
+      </c>
+      <c r="V4" s="7">
+        <v>45707</v>
+      </c>
+      <c r="W4" s="7">
+        <v>45708</v>
+      </c>
+      <c r="X4" s="7">
+        <v>45709</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>45710</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>45711</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>45712</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>45713</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>45714</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>45715</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>45716</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="4">
+        <f>COUNTIF(D5:AE5,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG5" s="4">
+        <f>COUNTIF(D5:AE5,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="4">
+        <f>COUNTIF(D5:AE5,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="11">
+        <f>AF5+AH5+AI5</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="31"/>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="20"/>
+      <c r="T6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="31"/>
+      <c r="W6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="4">
+        <f>COUNTIF(D6:AE6,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG6" s="4">
+        <f>COUNTIF(D6:AE6,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f>COUNTIF(D6:AE6,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f>COUNTBLANK(D6:AE6)</f>
+        <v>7</v>
+      </c>
+      <c r="AJ6" s="11">
+        <f t="shared" ref="AJ6:AJ10" si="1">AF6+AH6+AI6</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="20"/>
+      <c r="T7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="31"/>
+      <c r="W7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="4">
+        <f>COUNTIF(D7:AE7,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG7" s="4">
+        <f>COUNTIF(D7:AE7,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f>COUNTIF(D7:AE7,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI7" s="4">
+        <f>COUNTBLANK(D7:AE7)</f>
+        <v>7</v>
+      </c>
+      <c r="AJ7" s="11">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="31"/>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="20"/>
+      <c r="T8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" s="31"/>
+      <c r="W8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF8" s="4">
+        <f>COUNTIF(D8:AE8,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AG8" s="4">
+        <f>COUNTIF(D8:AE8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f>COUNTIF(D8:AE8,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AI8" s="4">
+        <f>COUNTBLANK(D8:AE8)</f>
+        <v>7</v>
+      </c>
+      <c r="AJ8" s="11">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="31"/>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="20"/>
+      <c r="T9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="31"/>
+      <c r="W9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF9" s="4">
+        <f>COUNTIF(D9:AE9,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AG9" s="4">
+        <f>COUNTIF(D9:AE9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="4">
+        <f>COUNTIF(D9:AE9,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AI9" s="4">
+        <f>COUNTBLANK(D9:AE9)</f>
+        <v>7</v>
+      </c>
+      <c r="AJ9" s="11">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="32"/>
+      <c r="I10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="21"/>
+      <c r="M10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="21"/>
+      <c r="T10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="32"/>
+      <c r="W10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF10" s="6">
+        <f>COUNTIF(D10:AE10,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AG10" s="6">
+        <f>COUNTIF(D10:AE10,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="6">
+        <f>COUNTIF(D10:AE10,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AI10" s="6">
+        <f>COUNTBLANK(D10:AE10)</f>
+        <v>7</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="Z5:Z10"/>
+    <mergeCell ref="Q5:Q10"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="H5:H10"/>
+    <mergeCell ref="V5:V10"/>
+    <mergeCell ref="E5:E10"/>
+    <mergeCell ref="L5:L10"/>
+    <mergeCell ref="S5:S10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D10 E5 L5 S5 Z5 F5:G10 M5:P10 T5:U10 AA5:AE10 I5:K10 H5 R5:R10 Q5 W5:Y10 V5">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D10 D3:AE4 E5 L5 S5 Z5 F5:G10 M5:P10 T5:U10 AA5:AE10 I5:K10 H5 R5:R10 Q5 W5:Y10 V5">
+    <cfRule type="expression" dxfId="35" priority="1">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFEC348B-0B0F-4C18-BABF-CCB291680EEF}">
+  <dimension ref="A1:AM17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="33" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="3.7109375" customWidth="1"/>
+    <col min="35" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="15"/>
+    </row>
+    <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="10" t="str">
+        <f>TEXT(D4,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="E3" s="10" t="str">
+        <f t="shared" ref="E3:AH3" si="0">TEXT(E4,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="F3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="H3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="I3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="K3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="L3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="M3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="N3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="O3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="P3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="R3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="S3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="T3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="U3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="V3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="W3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="X3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="Y3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="Z3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AA3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AB3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="AC3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AD3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AE3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AF3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="AG3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AH3" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AI3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7">
+        <v>45717</v>
+      </c>
+      <c r="E4" s="7">
+        <v>45718</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45719</v>
+      </c>
+      <c r="G4" s="7">
+        <v>45720</v>
+      </c>
+      <c r="H4" s="7">
+        <v>45721</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45722</v>
+      </c>
+      <c r="J4" s="7">
+        <v>45723</v>
+      </c>
+      <c r="K4" s="7">
+        <v>45724</v>
+      </c>
+      <c r="L4" s="7">
+        <v>45725</v>
+      </c>
+      <c r="M4" s="7">
+        <v>45726</v>
+      </c>
+      <c r="N4" s="7">
+        <v>45727</v>
+      </c>
+      <c r="O4" s="7">
+        <v>45728</v>
+      </c>
+      <c r="P4" s="7">
+        <v>45729</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>45730</v>
+      </c>
+      <c r="R4" s="7">
+        <v>45731</v>
+      </c>
+      <c r="S4" s="7">
+        <v>45732</v>
+      </c>
+      <c r="T4" s="7">
+        <v>45733</v>
+      </c>
+      <c r="U4" s="7">
+        <v>45734</v>
+      </c>
+      <c r="V4" s="7">
+        <v>45735</v>
+      </c>
+      <c r="W4" s="7">
+        <v>45736</v>
+      </c>
+      <c r="X4" s="7">
+        <v>45737</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>45738</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>45739</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>45740</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>45741</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>45742</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>45743</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>45744</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>45745</v>
+      </c>
+      <c r="AG4" s="7">
+        <v>45746</v>
+      </c>
+      <c r="AH4" s="7">
+        <v>45747</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH5" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" ref="AI5:AI11" si="1">COUNTIF(D5:AH5,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" ref="AJ5:AJ11" si="2">COUNTIF(D5:AH5,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" ref="AK5:AK11" si="3">COUNTIF(D5:AH5,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="11">
+        <f>AI5+AK5+AL5</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="20"/>
+      <c r="T6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="52"/>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" ref="AL6:AL11" si="4">COUNTBLANK(D6:AH6)</f>
+        <v>8</v>
+      </c>
+      <c r="AM6" s="11">
+        <f t="shared" ref="AM6:AM11" si="5">AI6+AK6+AL6</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="20"/>
+      <c r="T7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AM7" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="20"/>
+      <c r="T8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="36"/>
+      <c r="AF8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="52"/>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AM8" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="20"/>
+      <c r="T9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="4">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="AJ9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AM9" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
+        <v>6</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="35"/>
+      <c r="M10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="35"/>
+      <c r="T10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="37"/>
+      <c r="AF10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="52"/>
+      <c r="AI10" s="4">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="AJ10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK10" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AL10" s="4">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AM10" s="11">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="21"/>
+      <c r="F11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="21"/>
+      <c r="M11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="21"/>
+      <c r="T11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="21"/>
+      <c r="AH11" s="53"/>
+      <c r="AI11" s="6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="AJ11" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="6">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AM11" s="12">
+        <f t="shared" si="5"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="Z5:Z11"/>
+    <mergeCell ref="AG5:AG11"/>
+    <mergeCell ref="Y5:Y11"/>
+    <mergeCell ref="AE5:AE11"/>
+    <mergeCell ref="AH5:AH11"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AI3:AM3"/>
+    <mergeCell ref="E5:E11"/>
+    <mergeCell ref="L5:L11"/>
+    <mergeCell ref="S5:S11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5 L5 S5 AG5 D5:D11 F5:K11 M5:R11 T5:X11 Y5:Z5 AF5:AF11 AE5 AA5:AD11">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:AH4 E5 L5 S5 AG5 D5:D11 F5:K11 M5:R11 T5:X11 Y5:Z5 AF5:AF11 AE5 AA5:AD11">
+    <cfRule type="expression" dxfId="32" priority="5">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH5:AH11">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH5">
+    <cfRule type="expression" dxfId="30" priority="2">
+      <formula>AH$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5270A078-2837-43E3-9F3F-3F06D76D98CE}">
+  <dimension ref="A1:AL18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="33" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="5.7109375" customWidth="1"/>
+    <col min="38" max="38" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:38" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="15"/>
+    </row>
+    <row r="3" spans="1:38" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45" t="str">
+        <f>TEXT(D4,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="E3" s="46" t="str">
+        <f t="shared" ref="E3:AG3" si="0">TEXT(E4,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="F3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="G3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="H3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="I3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="J3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="K3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="L3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="M3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="N3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="O3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="P3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="Q3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="R3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="S3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="T3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="U3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="V3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="W3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="X3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="Y3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="Z3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AA3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AB3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AC3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="AD3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AE3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AF3" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="AG3" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AH3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="50"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="28">
+        <v>45748</v>
+      </c>
+      <c r="E4" s="7">
+        <v>45749</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45750</v>
+      </c>
+      <c r="G4" s="7">
+        <v>45751</v>
+      </c>
+      <c r="H4" s="7">
+        <v>45752</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45753</v>
+      </c>
+      <c r="J4" s="7">
+        <v>45754</v>
+      </c>
+      <c r="K4" s="7">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="7">
+        <v>45756</v>
+      </c>
+      <c r="M4" s="7">
+        <v>45757</v>
+      </c>
+      <c r="N4" s="7">
+        <v>45758</v>
+      </c>
+      <c r="O4" s="7">
+        <v>45759</v>
+      </c>
+      <c r="P4" s="7">
+        <v>45760</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>45761</v>
+      </c>
+      <c r="R4" s="7">
+        <v>45762</v>
+      </c>
+      <c r="S4" s="7">
+        <v>45763</v>
+      </c>
+      <c r="T4" s="7">
+        <v>45764</v>
+      </c>
+      <c r="U4" s="7">
+        <v>45765</v>
+      </c>
+      <c r="V4" s="7">
+        <v>45766</v>
+      </c>
+      <c r="W4" s="7">
+        <v>45767</v>
+      </c>
+      <c r="X4" s="7">
+        <v>45768</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>45769</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>45770</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>45771</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>45772</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>45773</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>45774</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>45775</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>45776</v>
+      </c>
+      <c r="AG4" s="39">
+        <v>45777</v>
+      </c>
+      <c r="AH4" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="3">
+        <f>COUNTIF(D5:AG5,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AI5" s="4">
+        <f>COUNTIF(D5:AG5,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f>COUNTIF(D5:AG5,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="11">
+        <f>AH5+AJ5+AK5</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="55"/>
+      <c r="H6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="20"/>
+      <c r="X6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="3">
+        <f>COUNTIF(D6:AG6,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AI6" s="4">
+        <f>COUNTIF(D6:AG6,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f>COUNTIF(D6:AG6,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f>COUNTBLANK(D6:AG6)</f>
+        <v>7</v>
+      </c>
+      <c r="AL6" s="11">
+        <f t="shared" ref="AL6:AL11" si="1">AH6+AJ6+AK6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="55"/>
+      <c r="H7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="20"/>
+      <c r="X7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="3">
+        <f>COUNTIF(D7:AG7,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AI7" s="4">
+        <f>COUNTIF(D7:AG7,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f>COUNTIF(D7:AG7,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AK7" s="4">
+        <f>COUNTBLANK(D7:AG7)</f>
+        <v>7</v>
+      </c>
+      <c r="AL7" s="11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="20"/>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W8" s="20"/>
+      <c r="X8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH8" s="3">
+        <f>COUNTIF(D8:AG8,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AI8" s="4">
+        <f>COUNTIF(D8:AG8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f>COUNTIF(D8:AG8,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AK8" s="4">
+        <f>COUNTBLANK(D8:AG8)</f>
+        <v>7</v>
+      </c>
+      <c r="AL8" s="11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="55"/>
+      <c r="H9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" s="20"/>
+      <c r="X9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH9" s="3">
+        <f>COUNTIF(D9:AG9,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AI9" s="4">
+        <f>COUNTIF(D9:AG9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="4">
+        <f>COUNTIF(D9:AG9,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="4">
+        <f>COUNTBLANK(D9:AG9)</f>
+        <v>7</v>
+      </c>
+      <c r="AL9" s="11">
+        <f t="shared" ref="AL9" si="2">AH9+AJ9+AK9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="55"/>
+      <c r="H10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="20"/>
+      <c r="J10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W10" s="20"/>
+      <c r="X10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH10" s="3">
+        <f>COUNTIF(D10:AG10,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AI10" s="4">
+        <f>COUNTIF(D10:AG10,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="4">
+        <f>COUNTIF(D10:AG10,"L")</f>
+        <v>3</v>
+      </c>
+      <c r="AK10" s="4">
+        <f>COUNTBLANK(D10:AG10)</f>
+        <v>7</v>
+      </c>
+      <c r="AL10" s="11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="56"/>
+      <c r="H11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="W11" s="21"/>
+      <c r="X11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="21"/>
+      <c r="AE11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="5">
+        <f>COUNTIF(D11:AG11,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AI11" s="6">
+        <f>COUNTIF(D11:AG11,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="6">
+        <f>COUNTIF(D11:AG11,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="AK11" s="6">
+        <f>COUNTBLANK(D11:AG11)</f>
+        <v>7</v>
+      </c>
+      <c r="AL11" s="12">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="I5:I11"/>
+    <mergeCell ref="P5:P11"/>
+    <mergeCell ref="W5:W11"/>
+    <mergeCell ref="AD5:AD11"/>
+    <mergeCell ref="D5:D11"/>
+    <mergeCell ref="E5:E11"/>
+    <mergeCell ref="G5:G11"/>
+    <mergeCell ref="A2:AL2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AH3:AL3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I5 P5 W5 AD5 J5:O11 F5:F11 Q5:V11 X5:AC11 AE5:AG11 H5:H11">
+    <cfRule type="cellIs" dxfId="27" priority="14" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="15" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:AG4 I5 P5 W5 AD5 J5:O11 F5:F11 Q5:V11 X5:AC11 AE5:AG11 H5:H11">
+    <cfRule type="expression" dxfId="25" priority="13">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D11">
+    <cfRule type="cellIs" dxfId="24" priority="9" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="23" priority="10">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E11">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="expression" dxfId="19" priority="6">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G11">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>G$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
